--- a/Inventario_Unificado.xlsx
+++ b/Inventario_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alejandro\Desktop\Elaris\UPC-Inventario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CB54E69-3C00-41C7-B5CF-8DB954A1420E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CF0A83-AEC9-4EB2-B19D-D0A645EA27C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2271B301-A178-4C84-BE62-10FBD7BB0815}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="138">
   <si>
     <t xml:space="preserve">N° DE EQUIPOS </t>
   </si>
@@ -436,6 +436,9 @@
   </si>
   <si>
     <t>00192185</t>
+  </si>
+  <si>
+    <t>IMAGE_PATH</t>
   </si>
 </sst>
 </file>
@@ -889,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C48EE0-AEAF-4B91-B815-61D886F51F93}">
-  <dimension ref="B2:G72"/>
+  <dimension ref="B2:H72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -897,10 +900,11 @@
     <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="75.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -917,10 +921,13 @@
         <v>4</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="168.75" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>4</v>
       </c>
@@ -936,11 +943,12 @@
       <c r="F3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="12"/>
+      <c r="H3" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>1</v>
       </c>
@@ -956,11 +964,12 @@
       <c r="F4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="12"/>
+      <c r="H4" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>1</v>
       </c>
@@ -976,11 +985,12 @@
       <c r="F5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="12"/>
+      <c r="H5" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>1</v>
       </c>
@@ -996,11 +1006,12 @@
       <c r="F6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="12"/>
+      <c r="H6" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>1</v>
       </c>
@@ -1016,11 +1027,12 @@
       <c r="F7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="202.5" x14ac:dyDescent="0.25">
+      <c r="G7" s="12"/>
+      <c r="H7" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="180" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>4</v>
       </c>
@@ -1036,11 +1048,12 @@
       <c r="F8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="146.25" x14ac:dyDescent="0.25">
+      <c r="G8" s="12"/>
+      <c r="H8" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="123.75" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>1</v>
       </c>
@@ -1056,11 +1069,12 @@
       <c r="F9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="146.25" x14ac:dyDescent="0.25">
+      <c r="G9" s="12"/>
+      <c r="H9" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="123.75" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1076,11 +1090,12 @@
       <c r="F10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="12"/>
+      <c r="H10" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>1</v>
       </c>
@@ -1096,11 +1111,12 @@
       <c r="F11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="12"/>
+      <c r="H11" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>1</v>
       </c>
@@ -1116,11 +1132,12 @@
       <c r="F12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="12"/>
+      <c r="H12" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>1</v>
       </c>
@@ -1136,11 +1153,12 @@
       <c r="F13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="12"/>
+      <c r="H13" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <v>1</v>
       </c>
@@ -1156,11 +1174,12 @@
       <c r="F14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="12"/>
+      <c r="H14" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>1</v>
       </c>
@@ -1176,11 +1195,12 @@
       <c r="F15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="12"/>
+      <c r="H15" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <v>1</v>
       </c>
@@ -1196,11 +1216,12 @@
       <c r="F16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="12"/>
+      <c r="H16" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <v>1</v>
       </c>
@@ -1216,11 +1237,12 @@
       <c r="F17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="12"/>
+      <c r="H17" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <v>1</v>
       </c>
@@ -1236,11 +1258,12 @@
       <c r="F18" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="12"/>
+      <c r="H18" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <v>1</v>
       </c>
@@ -1256,11 +1279,12 @@
       <c r="F19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="12"/>
+      <c r="H19" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <v>2</v>
       </c>
@@ -1276,11 +1300,12 @@
       <c r="F20" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="12"/>
+      <c r="H20" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="33.75" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <v>2</v>
       </c>
@@ -1296,11 +1321,12 @@
       <c r="F21" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G21" s="12"/>
+      <c r="H21" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <v>1</v>
       </c>
@@ -1316,11 +1342,12 @@
       <c r="F22" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G22" s="12"/>
+      <c r="H22" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <v>1</v>
       </c>
@@ -1336,11 +1363,12 @@
       <c r="F23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G23" s="12"/>
+      <c r="H23" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <v>1</v>
       </c>
@@ -1356,11 +1384,12 @@
       <c r="F24" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <v>1</v>
       </c>
@@ -1376,11 +1405,12 @@
       <c r="F25" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="G25" s="12"/>
+      <c r="H25" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <v>1</v>
       </c>
@@ -1396,11 +1426,12 @@
       <c r="F26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G26" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="G26" s="12"/>
+      <c r="H26" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B27" s="3">
         <v>1</v>
       </c>
@@ -1416,11 +1447,12 @@
       <c r="F27" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G27" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="G27" s="12"/>
+      <c r="H27" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
         <v>1</v>
       </c>
@@ -1436,11 +1468,12 @@
       <c r="F28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G28" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="12"/>
+      <c r="H28" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
         <v>1</v>
       </c>
@@ -1456,11 +1489,12 @@
       <c r="F29" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G29" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
         <v>1</v>
       </c>
@@ -1476,11 +1510,12 @@
       <c r="F30" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G30" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G30" s="12"/>
+      <c r="H30" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="56.25" x14ac:dyDescent="0.25">
       <c r="B31" s="3">
         <v>4</v>
       </c>
@@ -1494,11 +1529,12 @@
       <c r="F31" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G31" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="12"/>
+      <c r="H31" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="56.25" x14ac:dyDescent="0.25">
       <c r="B32" s="3">
         <v>1</v>
       </c>
@@ -1514,11 +1550,12 @@
       <c r="F32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G32" s="12"/>
+      <c r="H32" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="56.25" x14ac:dyDescent="0.25">
       <c r="B33" s="3">
         <v>1</v>
       </c>
@@ -1534,11 +1571,12 @@
       <c r="F33" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G33" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G33" s="12"/>
+      <c r="H33" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="3">
         <v>1</v>
       </c>
@@ -1552,11 +1590,12 @@
       <c r="F34" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G34" s="12"/>
+      <c r="H34" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="3">
         <v>1</v>
       </c>
@@ -1570,11 +1609,12 @@
       <c r="F35" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G35" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G35" s="12"/>
+      <c r="H35" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="3">
         <v>1</v>
       </c>
@@ -1588,11 +1628,12 @@
       <c r="F36" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G36" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G36" s="12"/>
+      <c r="H36" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="3">
         <v>1</v>
       </c>
@@ -1606,11 +1647,12 @@
       <c r="F37" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G37" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G37" s="12"/>
+      <c r="H37" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="3">
         <v>1</v>
       </c>
@@ -1624,11 +1666,12 @@
         <v>78</v>
       </c>
       <c r="F38" s="8"/>
-      <c r="G38" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G38" s="12"/>
+      <c r="H38" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
         <v>1</v>
       </c>
@@ -1642,11 +1685,12 @@
         <v>80</v>
       </c>
       <c r="F39" s="8"/>
-      <c r="G39" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="G39" s="12"/>
+      <c r="H39" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B40" s="3">
         <v>2</v>
       </c>
@@ -1658,11 +1702,12 @@
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="8"/>
-      <c r="G40" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G40" s="12"/>
+      <c r="H40" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="3">
         <v>4</v>
       </c>
@@ -1674,11 +1719,12 @@
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="8"/>
-      <c r="G41" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G41" s="12"/>
+      <c r="H41" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="3">
         <v>2</v>
       </c>
@@ -1690,11 +1736,12 @@
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="8"/>
-      <c r="G42" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="G42" s="12"/>
+      <c r="H42" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
         <v>4</v>
       </c>
@@ -1706,11 +1753,12 @@
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="8"/>
-      <c r="G43" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G43" s="12"/>
+      <c r="H43" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="3">
         <v>2</v>
       </c>
@@ -1722,11 +1770,12 @@
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="8"/>
-      <c r="G44" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G44" s="12"/>
+      <c r="H44" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="3">
         <v>1</v>
       </c>
@@ -1740,11 +1789,12 @@
         <v>91</v>
       </c>
       <c r="F45" s="8"/>
-      <c r="G45" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G45" s="12"/>
+      <c r="H45" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="3">
         <v>1</v>
       </c>
@@ -1758,11 +1808,12 @@
         <v>92</v>
       </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G46" s="12"/>
+      <c r="H46" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B47" s="3">
         <v>1</v>
       </c>
@@ -1776,11 +1827,12 @@
         <v>95</v>
       </c>
       <c r="F47" s="8"/>
-      <c r="G47" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G47" s="12"/>
+      <c r="H47" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B48" s="3">
         <v>1</v>
       </c>
@@ -1794,11 +1846,12 @@
         <v>96</v>
       </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G48" s="12"/>
+      <c r="H48" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B49" s="3">
         <v>1</v>
       </c>
@@ -1812,11 +1865,12 @@
         <v>97</v>
       </c>
       <c r="F49" s="8"/>
-      <c r="G49" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G49" s="12"/>
+      <c r="H49" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B50" s="3">
         <v>1</v>
       </c>
@@ -1830,11 +1884,12 @@
         <v>98</v>
       </c>
       <c r="F50" s="8"/>
-      <c r="G50" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G50" s="12"/>
+      <c r="H50" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B51" s="3">
         <v>1</v>
       </c>
@@ -1848,11 +1903,12 @@
         <v>101</v>
       </c>
       <c r="F51" s="8"/>
-      <c r="G51" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G51" s="12"/>
+      <c r="H51" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B52" s="3">
         <v>1</v>
       </c>
@@ -1866,11 +1922,12 @@
         <v>102</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G52" s="12"/>
+      <c r="H52" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B53" s="3">
         <v>1</v>
       </c>
@@ -1884,11 +1941,12 @@
         <v>104</v>
       </c>
       <c r="F53" s="8"/>
-      <c r="G53" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G53" s="12"/>
+      <c r="H53" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B54" s="3">
         <v>1</v>
       </c>
@@ -1902,11 +1960,12 @@
         <v>105</v>
       </c>
       <c r="F54" s="8"/>
-      <c r="G54" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G54" s="12"/>
+      <c r="H54" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="3">
         <v>1</v>
       </c>
@@ -1920,11 +1979,12 @@
         <v>108</v>
       </c>
       <c r="F55" s="8"/>
-      <c r="G55" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G55" s="12"/>
+      <c r="H55" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B56" s="3">
         <v>1</v>
       </c>
@@ -1938,11 +1998,12 @@
         <v>109</v>
       </c>
       <c r="F56" s="8"/>
-      <c r="G56" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G56" s="12"/>
+      <c r="H56" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="3">
         <v>2</v>
       </c>
@@ -1954,11 +2015,12 @@
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="8"/>
-      <c r="G57" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G57" s="12"/>
+      <c r="H57" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="3">
         <v>1</v>
       </c>
@@ -1974,11 +2036,12 @@
       <c r="F58" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G58" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G58" s="12"/>
+      <c r="H58" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B59" s="3">
         <v>1</v>
       </c>
@@ -1992,11 +2055,12 @@
         <v>116</v>
       </c>
       <c r="F59" s="8"/>
-      <c r="G59" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G59" s="12"/>
+      <c r="H59" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B60" s="3">
         <v>1</v>
       </c>
@@ -2010,11 +2074,12 @@
         <v>118</v>
       </c>
       <c r="F60" s="8"/>
-      <c r="G60" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G60" s="12"/>
+      <c r="H60" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B61" s="3">
         <v>1</v>
       </c>
@@ -2030,11 +2095,12 @@
       <c r="F61" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G61" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G61" s="12"/>
+      <c r="H61" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B62" s="3">
         <v>1</v>
       </c>
@@ -2050,11 +2116,12 @@
       <c r="F62" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G62" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="G62" s="12"/>
+      <c r="H62" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B63" s="3">
         <v>1</v>
       </c>
@@ -2068,11 +2135,12 @@
         <v>123</v>
       </c>
       <c r="F63" s="8"/>
-      <c r="G63" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G63" s="12"/>
+      <c r="H63" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64" s="3">
         <v>1</v>
       </c>
@@ -2086,11 +2154,12 @@
         <v>125</v>
       </c>
       <c r="F64" s="8"/>
-      <c r="G64" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G64" s="12"/>
+      <c r="H64" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B65" s="3">
         <v>1</v>
       </c>
@@ -2104,11 +2173,12 @@
         <v>126</v>
       </c>
       <c r="F65" s="8"/>
-      <c r="G65" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G65" s="12"/>
+      <c r="H65" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B66" s="3">
         <v>1</v>
       </c>
@@ -2122,11 +2192,12 @@
         <v>127</v>
       </c>
       <c r="F66" s="8"/>
-      <c r="G66" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G66" s="12"/>
+      <c r="H66" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B67" s="3">
         <v>1</v>
       </c>
@@ -2140,11 +2211,12 @@
         <v>128</v>
       </c>
       <c r="F67" s="8"/>
-      <c r="G67" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G67" s="12"/>
+      <c r="H67" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B68" s="3">
         <v>2</v>
       </c>
@@ -2156,11 +2228,12 @@
       </c>
       <c r="E68" s="10"/>
       <c r="F68" s="8"/>
-      <c r="G68" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G68" s="12"/>
+      <c r="H68" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B69" s="3">
         <v>1</v>
       </c>
@@ -2176,11 +2249,12 @@
       <c r="F69" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="G69" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G69" s="12"/>
+      <c r="H69" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B70" s="3">
         <v>1</v>
       </c>
@@ -2194,11 +2268,12 @@
         <v>133</v>
       </c>
       <c r="F70" s="8"/>
-      <c r="G70" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G70" s="12"/>
+      <c r="H70" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B71" s="3">
         <v>1</v>
       </c>
@@ -2212,11 +2287,12 @@
         <v>135</v>
       </c>
       <c r="F71" s="8"/>
-      <c r="G71" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G71" s="12"/>
+      <c r="H71" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B72" s="3">
         <v>1</v>
       </c>
@@ -2230,7 +2306,8 @@
         <v>136</v>
       </c>
       <c r="F72" s="8"/>
-      <c r="G72" s="12" t="s">
+      <c r="G72" s="12"/>
+      <c r="H72" s="12" t="s">
         <v>79</v>
       </c>
     </row>
